--- a/artfynd/A 11213-2022 artfynd.xlsx
+++ b/artfynd/A 11213-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11213-2022 artfynd.xlsx
+++ b/artfynd/A 11213-2022 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>99564945</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595778.4600258654</v>
+        <v>595779</v>
       </c>
       <c r="R14" t="n">
-        <v>6912463.877241801</v>
+        <v>6912464</v>
       </c>
       <c r="S14" t="n">
         <v>48</v>
@@ -2097,19 +2097,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,7 +2241,7 @@
         <v>99564934</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595782.0215915864</v>
+        <v>595782</v>
       </c>
       <c r="R16" t="n">
-        <v>6912420.737332884</v>
+        <v>6912421</v>
       </c>
       <c r="S16" t="n">
         <v>48</v>
@@ -2326,19 +2316,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 11213-2022 artfynd.xlsx
+++ b/artfynd/A 11213-2022 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>99564945</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>99564934</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 11213-2022 artfynd.xlsx
+++ b/artfynd/A 11213-2022 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>99564945</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>99564934</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 11213-2022 artfynd.xlsx
+++ b/artfynd/A 11213-2022 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>99564945</v>
       </c>
       <c r="B14" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>99564934</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 11213-2022 artfynd.xlsx
+++ b/artfynd/A 11213-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99564946</v>
+        <v>370260</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>1352</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännåsen, Mpd</t>
+          <t>SVARTTJÄRNEN (17H2a07), Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595743.4284590735</v>
+        <v>593951</v>
       </c>
       <c r="R2" t="n">
-        <v>6912337.333888129</v>
+        <v>6912401</v>
       </c>
       <c r="S2" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>170720071 / RAM SINE / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,69 +761,78 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Skogliga småvatten /</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gammal grov asp</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Kent Wallin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99564944</v>
+        <v>2100008</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännåsen, Mpd</t>
+          <t>SVARTTJÄRNEN (17H2a07), Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595280.9125479215</v>
+        <v>593951</v>
       </c>
       <c r="R3" t="n">
-        <v>6912292.529634375</v>
+        <v>6912401</v>
       </c>
       <c r="S3" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>170720071 / LEP SATU / Tämligen allmän (2)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +877,40 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skogliga småvatten /</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal grov asp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Kent Wallin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99564937</v>
+        <v>99564941</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595718.462900955</v>
+        <v>595712</v>
       </c>
       <c r="R4" t="n">
-        <v>6912331.040771263</v>
+        <v>6912346</v>
       </c>
       <c r="S4" t="n">
         <v>48</v>
@@ -972,19 +975,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99564923</v>
+        <v>99564925</v>
       </c>
       <c r="B5" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595468.7437919002</v>
+        <v>595476</v>
       </c>
       <c r="R5" t="n">
-        <v>6912221.153764501</v>
+        <v>6912245</v>
       </c>
       <c r="S5" t="n">
         <v>48</v>
@@ -1084,19 +1072,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99564927</v>
+        <v>99564937</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595451.5082853716</v>
+        <v>595718</v>
       </c>
       <c r="R6" t="n">
-        <v>6912384.801054608</v>
+        <v>6912331</v>
       </c>
       <c r="S6" t="n">
         <v>48</v>
@@ -1196,19 +1169,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1198,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99564931</v>
+        <v>99564939</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595438.9989911841</v>
+        <v>595420</v>
       </c>
       <c r="R7" t="n">
-        <v>6912382.584794725</v>
+        <v>6912379</v>
       </c>
       <c r="S7" t="n">
         <v>48</v>
@@ -1308,19 +1266,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99564925</v>
+        <v>99564935</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595476.4437787337</v>
+        <v>595713</v>
       </c>
       <c r="R8" t="n">
-        <v>6912245.08772236</v>
+        <v>6912346</v>
       </c>
       <c r="S8" t="n">
         <v>48</v>
@@ -1420,19 +1363,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1392,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99564928</v>
+        <v>99564923</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595582.6011734826</v>
+        <v>595469</v>
       </c>
       <c r="R9" t="n">
-        <v>6912474.092091525</v>
+        <v>6912221</v>
       </c>
       <c r="S9" t="n">
         <v>48</v>
@@ -1532,19 +1460,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1489,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99564932</v>
+        <v>99564933</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595581.4055642756</v>
+        <v>595466</v>
       </c>
       <c r="R10" t="n">
-        <v>6912483.357140777</v>
+        <v>6912259</v>
       </c>
       <c r="S10" t="n">
         <v>48</v>
@@ -1644,19 +1557,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1586,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99564930</v>
+        <v>99564932</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595546.9585193637</v>
+        <v>595582</v>
       </c>
       <c r="R11" t="n">
-        <v>6912287.086805391</v>
+        <v>6912483</v>
       </c>
       <c r="S11" t="n">
         <v>48</v>
@@ -1756,19 +1654,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1683,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99564943</v>
+        <v>99564946</v>
       </c>
       <c r="B12" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1718,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595659.09430371</v>
+        <v>595743</v>
       </c>
       <c r="R12" t="n">
-        <v>6912339.109678851</v>
+        <v>6912337</v>
       </c>
       <c r="S12" t="n">
         <v>48</v>
@@ -1868,19 +1751,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1780,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99564940</v>
+        <v>99564927</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1815,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595470.5255192126</v>
+        <v>595452</v>
       </c>
       <c r="R13" t="n">
-        <v>6912223.994488954</v>
+        <v>6912385</v>
       </c>
       <c r="S13" t="n">
         <v>48</v>
@@ -1980,19 +1848,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,55 +1877,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99564945</v>
+        <v>99564931</v>
       </c>
       <c r="B14" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brännåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595779</v>
+        <v>595439</v>
       </c>
       <c r="R14" t="n">
-        <v>6912464</v>
+        <v>6912382</v>
       </c>
       <c r="S14" t="n">
         <v>48</v>
@@ -2126,37 +1974,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99564936</v>
+        <v>99564940</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595471.9213900227</v>
+        <v>595471</v>
       </c>
       <c r="R15" t="n">
-        <v>6912224.034264626</v>
+        <v>6912224</v>
       </c>
       <c r="S15" t="n">
         <v>48</v>
@@ -2199,19 +2042,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,15 +2071,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99564934</v>
+        <v>99564926</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,39 +2082,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brännåsen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595782</v>
+        <v>595657</v>
       </c>
       <c r="R16" t="n">
-        <v>6912421</v>
+        <v>6912340</v>
       </c>
       <c r="S16" t="n">
         <v>48</v>
@@ -2345,37 +2168,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99564924</v>
+        <v>99564928</v>
       </c>
       <c r="B17" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595505.2006268308</v>
+        <v>595583</v>
       </c>
       <c r="R17" t="n">
-        <v>6912265.436834001</v>
+        <v>6912474</v>
       </c>
       <c r="S17" t="n">
         <v>48</v>
@@ -2418,19 +2236,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,15 +2265,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99564926</v>
+        <v>99564930</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,10 +2300,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595657.1934100311</v>
+        <v>595547</v>
       </c>
       <c r="R18" t="n">
-        <v>6912340.450337817</v>
+        <v>6912287</v>
       </c>
       <c r="S18" t="n">
         <v>48</v>
@@ -2530,19 +2333,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,37 +2362,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99564933</v>
+        <v>99564936</v>
       </c>
       <c r="B19" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2609,10 +2397,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595465.3450126103</v>
+        <v>595472</v>
       </c>
       <c r="R19" t="n">
-        <v>6912258.721109796</v>
+        <v>6912224</v>
       </c>
       <c r="S19" t="n">
         <v>48</v>
@@ -2642,19 +2430,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,37 +2459,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99564942</v>
+        <v>99564938</v>
       </c>
       <c r="B20" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2721,10 +2494,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595451.5744691773</v>
+        <v>595794</v>
       </c>
       <c r="R20" t="n">
-        <v>6912382.478090141</v>
+        <v>6912422</v>
       </c>
       <c r="S20" t="n">
         <v>48</v>
@@ -2754,19 +2527,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,12 +2559,7 @@
         <v>99564929</v>
       </c>
       <c r="B21" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,10 +2591,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595509.0950829939</v>
+        <v>595509</v>
       </c>
       <c r="R21" t="n">
-        <v>6912259.503016504</v>
+        <v>6912259</v>
       </c>
       <c r="S21" t="n">
         <v>48</v>
@@ -2866,19 +2624,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2905,37 +2653,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99564938</v>
+        <v>99564942</v>
       </c>
       <c r="B22" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2945,10 +2688,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595794.0918679656</v>
+        <v>595452</v>
       </c>
       <c r="R22" t="n">
-        <v>6912422.012381156</v>
+        <v>6912383</v>
       </c>
       <c r="S22" t="n">
         <v>48</v>
@@ -2978,19 +2721,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,15 +2750,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99564939</v>
+        <v>99564934</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,34 +2761,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brännåsen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595420.0288524196</v>
+        <v>595782</v>
       </c>
       <c r="R23" t="n">
-        <v>6912378.324677907</v>
+        <v>6912421</v>
       </c>
       <c r="S23" t="n">
         <v>48</v>
@@ -3090,19 +2823,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,15 +2852,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99564941</v>
+        <v>99564945</v>
       </c>
       <c r="B24" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3145,34 +2863,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Brännåsen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595711.9895855145</v>
+        <v>595779</v>
       </c>
       <c r="R24" t="n">
-        <v>6912345.735149743</v>
+        <v>6912464</v>
       </c>
       <c r="S24" t="n">
         <v>48</v>
@@ -3202,19 +2925,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,15 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99564935</v>
+        <v>99564944</v>
       </c>
       <c r="B25" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3257,21 +2965,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3281,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595713.3854063898</v>
+        <v>595281</v>
       </c>
       <c r="R25" t="n">
-        <v>6912345.775026423</v>
+        <v>6912293</v>
       </c>
       <c r="S25" t="n">
         <v>48</v>
@@ -3314,19 +3022,9 @@
           <t>2022-03-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-03-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3350,6 +3048,200 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>99564943</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brännåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595659</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6912339</v>
+      </c>
+      <c r="S26" t="n">
+        <v>48</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>99564924</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brännåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>595505</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6912265</v>
+      </c>
+      <c r="S27" t="n">
+        <v>48</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-03-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11213-2022 artfynd.xlsx
+++ b/artfynd/A 11213-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564925</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564937</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564939</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564935</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/370260</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564923</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564933</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564932</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564946</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2100008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1874,6 +1934,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564927</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,6 +2036,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564931</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564940</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2165,6 +2240,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564926</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2262,6 +2342,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564928</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2359,6 +2444,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564930</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,6 +2546,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564936</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2553,6 +2648,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564938</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2650,6 +2750,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564929</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2747,6 +2852,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564942</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2849,6 +2959,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564934</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2951,6 +3066,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564945</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3048,6 +3168,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564944</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3145,6 +3270,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564943</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3242,8 +3372,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99564924</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>